--- a/src/test/resources/TEST_DATA/LyceumData.xlsx
+++ b/src/test/resources/TEST_DATA/LyceumData.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Lyceum Leaf International School</t>
   </si>
   <si>
-    <t>TP002522</t>
+    <t>LPA007787</t>
   </si>
   <si>
     <t xml:space="preserve">Second page invocation successful</t>
@@ -94,10 +94,10 @@
   <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,16 +623,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -640,19 +640,19 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/src/test/resources/TEST_DATA/LyceumData.xlsx
+++ b/src/test/resources/TEST_DATA/LyceumData.xlsx
@@ -45,13 +45,13 @@
     <t xml:space="preserve">Lyceum Leaf International School</t>
   </si>
   <si>
-    <t>DLAV000169</t>
+    <t>DLAV000166</t>
   </si>
   <si>
     <t xml:space="preserve">Second page invocation successful</t>
   </si>
   <si>
-    <t xml:space="preserve">0167 5100 0128</t>
+    <t xml:space="preserve">1049 5334 8269</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
       <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
